--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Durapallam_13.457935_80.112684.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Durapallam_13.457935_80.112684.xlsx
@@ -566,6 +566,11 @@
           <t>109</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -573,6 +578,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1A1, 1A10, 1A2, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 2K, 2L, 2M, 2N, 3A1A, 3A1B, 3A2A, 3A2B, 3A3A, 3A3B, 3B1, 3B2, 3C, 4A1A, 4A2A, 4A2A1, 4A2B, 4A2C, 4B1, 4B2, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -580,6 +590,11 @@
           <t>110</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A1, 15A2, 15B, 15C, 15D1, 15D2, 15E, 15F1, 15F2, 15F3, 1A, 1B1, 1B2, 2A, 2B, 3A, 3B1, 3B2, 4A, 4B, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -587,6 +602,11 @@
           <t>111</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -594,6 +614,11 @@
           <t>112</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -601,6 +626,11 @@
           <t>113</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -608,6 +638,11 @@
           <t>114</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -615,6 +650,11 @@
           <t>115</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -622,6 +662,11 @@
           <t>116</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -629,6 +674,11 @@
           <t>117</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -636,6 +686,11 @@
           <t>118</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -643,6 +698,11 @@
           <t>119</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -650,6 +710,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 3C1, 3C2, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -657,6 +722,11 @@
           <t>120</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -664,6 +734,11 @@
           <t>121</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -671,6 +746,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -678,6 +758,11 @@
           <t>123</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -685,6 +770,11 @@
           <t>124</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -692,6 +782,11 @@
           <t>125</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -699,6 +794,11 @@
           <t>126</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -706,6 +806,11 @@
           <t>127</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2, 3, 4A, 4B, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -713,6 +818,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -720,6 +830,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -727,6 +842,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -734,6 +854,11 @@
           <t>130</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -741,6 +866,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2A1, 2B2B, 2B2C, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -748,6 +878,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1B, 1A2, 1B, 1C, 1D, 2A1, 2A2, 2B, 2C, 2D, 2E, 2F, 2G, 2H1, 2H2, 2H3, 2I, 2J1A1, 2J2, 2J3, 2J4, 3A, 3B1, 3B2, 3C1, 3C2, 3C3, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -755,6 +890,11 @@
           <t>133</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -762,6 +902,11 @@
           <t>134</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -769,6 +914,11 @@
           <t>135</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -776,6 +926,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A1, 2A2, 2B1A, 2B1B1, 2B1B2, 2B1B3, 2B2, 2C1A, 2C1B, 2C2, 4, 5A, 5B, 5C1, 5C2, 5C3, 5D1, 5D2A, 5D2B, 5E1A, 5E1B, 5E2, 5F, 5G1, 5G2, 5H1, 5H2, 5I, 5J, 6</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -783,6 +938,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -790,6 +950,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -797,6 +962,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -804,6 +974,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -811,6 +986,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -818,6 +998,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -825,6 +1010,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -832,6 +1022,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -839,6 +1034,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -846,6 +1046,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -853,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -860,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B1C, 2B2, 3A, 3B, 4A, 4B1, 4B1B, 4B1C, 4B1D, 4B1E, 4B2, 4B3, 5A, 5B, 5C, 5D, 5E, 6A, 6B, 6C</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -867,6 +1082,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A, 2B1A, 2B1B, 2B2, 2C1, 2C2, 2C3</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -874,6 +1094,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -881,6 +1106,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -888,6 +1118,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -895,6 +1130,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -902,6 +1142,11 @@
           <t>152</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B, 4C1, 4C2, 4D, 4E, 4F, 5A1, 5A2A, 5A2B, 5A3, 5A4, 5A5, 5A6, 5B1, 5B2A, 5B2B, 5B3, 5B4, 5B5, 5B6A, 5B6B, 5B6C, 6A, 6B, 6C, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -909,6 +1154,11 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14A, 14B, 15A, 15B, 16A1, 16A2, 16B, 17A, 17B, 18, 19A, 19B, 20, 21, 22, 2A1A1, 2A1B1A1, 2A1B1A2, 2A1B1B, 2A1B1C1, 2A1B1C2, 2A1B2, 2A1B3A1, 2A1B3A2, 2A1B3B1, 2A1B3B2, 2A1B3B3, 2A1B3B4, 2A1B3C1A, 2A2A1, 2A2A2, 2A2A3, 2A2A4, 2A2B1, 2A2B2, 2B, 3A1A1, 3A1B1, 3A1B2, 3A2A1, 3A2A3, 3A2B, 3A3, 3B, 3C1A, 3C1B, 3C2, 4, 5, 6, 7, 9</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -916,6 +1166,11 @@
           <t>154</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -923,6 +1178,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 18, 19, 1A, 1B1A1, 1B1A2, 1B1B, 1B2, 29, 2A1A, 2A1B, 2A2, 2B1A1A, 2B1A2, 2B1B1A, 2B1B1B, 2B1B1C, 2B1B1D, 2B1B1E, 2B1B2, 2B1C1, 2B1C2, 2B2, 2B3, 2B4, 30, 3A1A, 3A1B1A, 3A1B1B, 3A1B2, 3A1B3A, 3A1B4A, 3A1C1A, 3A1C1B1A1, 3A1C1B1A2, 3A1C1B2, 3A1C2, 3A1C3A1, 3A1C4, 3A1C5, 3A1C6A1A, 3A1C6A2, 3A1C6B, 3A1C7A, 3A1C7B, 3A1C7C1A, 3A1C7C2, 3A2A, 3A2B, 3A2C, 3B1A, 3B1B, 3B1C, 3B1D, 3B1E, 3B1F, 3B1G, 3B1H, 3B1I, 3B1J, 3B1K, 3B2, 3B3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -930,6 +1190,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -937,6 +1202,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -944,6 +1214,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 10A1A, 10A2, 10A3A, 10A3B, 10B, 11A1A, 11A2, 11B, 12, 13, 2, 3, 4A1A, 4A1B, 4A2, 4A3, 4A4A, 4A4B, 4B1, 4B2, 4C1, 4C2, 5A1, 5A2, 5B, 5C, 6A, 6B, 7A, 7B, 8A1, 8A2, 8A3, 8B1, 8B2, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -951,6 +1226,11 @@
           <t>159</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1A1A1A1, 1A1A2, 1A1A3, 1A1A4, 1A1B1A, 1A1B2, 1A1C1, 1A1C2, 1A2A, 1A2B, 1A3A, 1A3B, 1B1A, 1B1B, 1B2, 1B3, 1B4, 1B5, 2A1A, 2A1B, 2A2, 2B1, 2B2, 2B3, 2B4, 2B5, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -958,6 +1238,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B, 2C, 2D1, 2D2, 2E1A1, 2E1A2, 2E1B, 2E2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -965,6 +1250,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12A, 12B, 13A, 13B, 14A, 14B, 15, 16, 17, 18, 19A, 19B, 1A, 1B, 1C, 1D, 2, 20A1, 20A2, 20A3A, 20B, 21A, 21B, 22, 23A, 23B, 23C, 24A, 24B, 24C, 24D, 24E, 24F, 25, 3A, 3B, 4A, 4B, 4C, 5A1, 5A2, 5B, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9A, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -972,6 +1262,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2A, 1A2B, 1A2C, 1A3A1A, 1A3A2, 1A3B1, 1A3C1A, 1A3C2, 1A3C3, 1B1, 1B2, 20, 21, 22, 23, 24, 25, 26, 2A1A, 2A1B, 2A2A, 2A2B, 2B, 3A1A1, 3A1A2, 3A1B, 3A2A, 3A2B, 3A3A1A, 3A3A2, 3A3B, 3B, 4, 5, 6A1A1, 6A1B, 6A1C, 6A1D, 6A1E, 6A2, 6A3, 6B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -979,6 +1274,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 1A1A2, 1A1B, 1A2, 1A3, 1B, 20, 21, 22, 23, 24, 25, 26, 2A1, 2A2, 2B1, 2B2, 2B3, 3A1A1, 3A1A1A1A, 3A1A2A, 3A1A2B, 3A1A2C, 3A1A2D, 3A1B, 3A1C1A1, 3A1C1B, 3A1C2A, 3A1D1A1, 3A1E, 3A2, 3B1A, 3B1B, 3B2, 4, 4A1, 4A2, 4A3, 4B, 4C1, 4C2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -986,6 +1286,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A1A, 1A1B, 1A2, 1B1A1A, 1B1A2, 1B1A3, 1B1B, 1B1C, 1B2, 2A1, 2A2, 2B, 3A10, 3A1A1A1, 3A1B, 3A2, 3A3, 3A4, 3A5, 3A6, 3A7, 3A8, 3A9, 3B, 4A1, 4A2A, 4A3A, 4A3B, 4A3C, 4A3D, 4B, 5, 6A1, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -993,6 +1298,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1000,6 +1310,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2A1, 1B2A3, 1B2A4, 1B2B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1007,6 +1322,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13, 14A1, 14B, 14C, 14D, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9A1A, 9A1B, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1014,6 +1334,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1021,6 +1346,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1028,6 +1358,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1035,6 +1370,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 2A, 2B, 3A, 3B, 4A, 4B1, 4B2A, 4B2B1A, 4B2B2, 4B3, 4C, 4D, 5A, 5B, 6A, 6B1A1A1, 6B1B, 6B1C, 6B2, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1042,6 +1382,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1049,6 +1394,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1056,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1063,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1070,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19A, 19B, 19C, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29A, 29B, 2A, 2A1, 2A1A1A, 2A1A1A3, 2A1A1B, 2A1A2, 2A1B, 2B, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38A, 38B, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1077,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1A, 2, 40, 41, 42, 43, 44, 45, 46, 47, 51</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1084,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1091,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1B1A1, 1B1A2, 1B1B, 1B1C, 1B1D, 1B1E, 1B1F, 1B1G, 1B1H, 1B2A, 1B2B, 1B3, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1098,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1105,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1112,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1A3, 1B1A1, 1B1A1A, 1B1A2, 1B1A4, 1B1A5, 1B1A6, 1B1A7, 1B1A8, 1B1A9, 1B1C, 1B1D, 1B2A1, 1B2B, 1B2C, 1B2D, 1B3A, 20, 21, 22A, 22B, 23A, 23B, 24, 25, 26, 27, 28, 29, 2A, 2B, 2E, 2F, 3, 30, 31, 32, 33A1, 33B, 34A1, 34B, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 6A, 6B, 7, 70, 71, 72, 73, 74, 75, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1119,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1126,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1133,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 2A1, 2A2, 2B, 3A1, 3A2, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1140,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1147,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1154,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1161,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B2, 1C1, 1C2, 2A1A, 2A1B1, 2A1B2, 2A2A, 2A2B, 2B1A, 2B1B, 2B2A1A, 2B2A2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1168,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2B3, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1175,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1182,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C, 2D, 2E, 2F1, 2F2, 3A, 3B, 3C, 3D, 4</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1189,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 19A, 19B, 1A1A, 1A1A2A, 1A2, 1A3, 1B1, 1B1B, 1B1C, 1B2, 1B3, 1C1, 1C2A1, 1C2A1C, 1C2A2, 1C2B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A1B, 2A1C, 2A2, 2A3, 2B, 2C, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A1A, 3A2, 3B1, 3B2, 3B3, 3B4, 3C, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1A, 4A2, 4A3, 4A4, 4B1A1, 4B2, 4C, 4D, 50, 51, 52, 53, 5A1, 5A1A1, 5A2, 5B, 5B1A1A1A, 5B2, 5C1, 5C2, 5C3, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1196,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1203,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1210,11 +1670,21 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Durapallam_13.457935_80.112684.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Durapallam_13.457935_80.112684.xlsx
@@ -1694,6 +1694,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1701,6 +1706,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H1, 1H2, 2A1A1, 2A1A2, 2A1A3, 2A1B, 2A2, 2A3A, 2A3B, 2B1, 2B2A, 2B2B, 2B2C, 2B3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1708,6 +1718,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A1A, 4A2, 4A3, 4A4, 4B1, 4B2, 5</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1715,6 +1730,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1722,6 +1742,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 17C, 18A, 18B, 18C, 18D, 18E, 18F1, 18F2, 19A1, 19A2A, 19A2B, 19A3, 2, 20, 21, 22, 23, 24, 25, 26, 27A1A, 27A1B, 27B, 27C, 28, 29, 3, 30, 31, 32A, 32B, 33, 34, 35, 36, 37, 38, 39A, 39B, 39C, 4, 40, 5, 6A, 6B, 6C, 6D, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1729,6 +1754,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1736,6 +1766,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 12, 13A, 13B, 14A, 14B, 15, 16A, 16B, 2, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1743,6 +1778,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1750,6 +1790,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>100, 101, 102, 10A, 10B, 11, 12A, 12B, 12C, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B, 1A1C1, 1A1C2, 1A1D1A1A1, 1A1D1A1A1A, 1A1D1A1A3, 1A1D1A1A5, 1A1D1A1A6A, 1A1D1A1B, 1A1D1A1C, 1A1D1A1D, 1A1D1A2, 1A1D1A2A2A, 1A1D1B1, 1A1D1B2, 1A1D1C, 1A1D1D, 1A1D1E, 1A1D1F1, 1A1D1F2, 1A1D1F3, 1A1D1G, 1A1D2, 1A1D3, 1A1D4, 1A1D5, 1A1D6, 1A1D7A1A1A, 1A1D7B, 1A1D8, 1A1DE1A, 1A1DE1B, 1A2, 1A3A, 1A4, 1A5A1, 1A5A2A1, 1A5A2B, 1A5B, 1B1A1A, 1B1A2, 1B1B1, 1B1B2, 1B1B2B, 1B1B3A, 1B1B3B, 1B1B3C, 1B1B4A, 1B1B5, 1B1B6, 1B3A, 1B3B1A, 1B3B2A, 2, 20A, 20B, 21, 22A, 22B, 23, 24A1A, 24A1B, 24A2, 24A3, 24A4, 24A5, 24B, 24C, 25A, 25B, 26A, 26B, 26C, 26D, 26E, 26F, 26G, 26H, 26J, 27, 28A, 28B, 29, 2A1D7C1A1, 3, 30, 31, 32, 33, 34, 35, 36, 37A, 37B, 37C, 38, 39, 4, 40, 41, 42, 43, 44A, 44B, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A, 5B, 5C, 6, 60, 61, 62, 63A, 63B, 64, 65, 66, 67, 68, 69, 70, 71, 72A1, 72A2, 72B, 73, 74, 75, 76, 77, 78, 79, 7A1A1A, 7A1A2, 7A1A3, 7A1A4, 7A1A5, 7A1B, 7A2, 7B, 7C, 7D, 7E, 7F, 8, 80, 81, 82, 83A1A1, 83A1A2, 83A1B1, 83A1B2, 83A1C, 83A2, 83A3, 83B, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1757,6 +1802,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B1, 1A1B2, 1A2, 1B1A, 1B1B, 1B1C, 1B2, 1C1A, 1C1B, 1C2, 1D1, 1D2, 1D3, 1E1A1A, 1E1A1B, 1E1A2, 1E1A3, 1E1B, 1E2, 1F, 20, 2A1A, 2A1B, 2A2, 2B1A1, 2B1B, 2B2, 2C, 2D1A, 2D1B, 2D2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1764,6 +1814,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A1, 14B, 14C, 14D, 15, 16, 17A, 17B, 18, 19, 1A, 1B, 1C, 1D, 2, 20A, 20B, 3, 4, 5A, 5B, 6A, 6B, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1771,6 +1826,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1778,6 +1838,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1785,6 +1850,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2B1, 2B1B1, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1792,6 +1862,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A1A1, 1A1B, 1A1C, 1A2, 1A3A, 1A3A2, 1B, 2A1, 2A2, 2B, 3A1, 3A2, 3B1, 3B1B, 3B1C, 3B2A, 3B2B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1799,6 +1874,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1806,6 +1886,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1813,6 +1898,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1820,6 +1910,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A, 1B1A1, 1B1A2, 1B1B, 1B2, 2A1, 2A2, 2A3, 2A4, 2B1, 2B2, 2B3, 2B4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1827,6 +1922,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1A1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1834,6 +1934,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A1A1A1A, 1A1A1B, 1A1B, 1A2, 1B, 1C, 2A1A, 2A2, 2A3A1A1, 2A3A2, 2A3B, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1841,6 +1946,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1848,6 +1958,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1855,6 +1970,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 16A, 16B, 17A, 17A1, 17B1A, 17B1B, 18A, 18B, 18C, 19A, 19B, 1A1, 1A1A1A1, 1A1A1A2, 1A1A1B, 1A1A1C, 1A1A1C1, 1A1A1C1B, 1A1A1D, 1A1A1E1, 1A1A2C1, 1A1A3A1, 1A1A3B, 1A1B, 1A1C1B, 1A1C2A1, 1A1C2B, 1A2A1, 1A2A1A1, 1A2A2, 1A2B1, 1A2B1A1, 1A2B2, 1A3A1, 1A3B, 1A4A1A, 1A4A2, 1A4B1, 1A4B2, 1A4B3, 1B1A1A, 1B2A, 1B3, 1C1A, 1C1B, 1C1C, 1C1D, 1C2A1A, 1C2A1B, 1C2B1A, 1C2B1B, 2, 20A, 20B, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33A, 33B, 34, 35, 36A, 36B, 37A, 37B, 37C, 38, 39, 40, 41, 42, 43, 44, 45A, 45B, 45C, 45D, 45E, 46A1, 46A2A, 46A2B, 47, 48, 49, 4A, 4B, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1862,6 +1982,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A1A1A, 1A1A2, 1A1B1A, 1A1B1B, 1A1B2, 1A1C1A1, 1A1C2A, 1A1D, 1A2, 1AAC2B, 1B1A1, 1B1A2, 1B1B, 1B2A, 1B2B, 1C1A1, 1C1B, 1C1C, 1C1D, 1C1E, 1C1F, 1C2A, 1C2B, 1C3A, 1C3B, 2A1A1, 2A1A2, 2A1B, 2A2, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1869,6 +1994,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1A, 1A1B1, 1A1C1, 1A1C2, 1A2, 1A3A1, 1A3B, 1B1, 1B2A, 1B2B, 1B3, 20, 21, 22, 23, 24, 2A1A1A, 2A1A2, 2A1B, 2A2, 2A3A, 2A3B, 2B, 2C1, 2C2, 3A1A, 3A1B, 3A2, 3B1A1, 3B1A2, 3B1B, 3B2A, 3B2B, 3B3, 4A1, 4A2A1A, 4A2B, 4A2C, 4A3A, 4A3B, 4B1A, 4B1B, 4B1C1, 4B2A1A, 4B2B, 4C1, 4C2, 5A, 5B, 5C, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1876,6 +2006,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A1A2, 1A1B, 1A1C1, 1A1C2, 1A1D, 1A1E, 1A1F1, 1A1F2, 1A1G1, 1A1G2, 1A1H1, 1A2A, 1A2B, 1A2C, 1A2D, 1B1A, 1B1B1, 1B1B2, 1B2A, 1B2B, 2A, 2B, 3A1, 3A2, 3B1, 3B2, 4, 4A1A, 4A1B, 4B1, 4B2, 5, 5A, 5B, 6, 6A1, 6A2, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1883,6 +2018,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 1A1A1A, 1A1B2, 1A1C1, 1A1D1, 1A1D1A1, 1A1D1A2, 1A1D1B1, 1A1D1B3A1A, 1A1D1B3A1B, 1A1D1B3A1C, 1A1D1B3A2, 1A1D2A1, 1A1D2B, 1A1D2C, 1A1D2D, 1A1D2E, 1A1D2F, 1A2, 1B1, 1B2, 26, 27, 28, 29, 2A1A1A1, 2A1A2, 2A1B, 2A2A, 2A2B, 2A2C1A, 2A2C1B, 2A2C2, 2A2C3, 2B, 2C1A1A1, 2C2, 2C3, 30, 31, 32, 33, 34A, 34B, 35, 37, 38, 39, 3A, 3B, 3C1, 3C2, 40, 41, 42A, 42B, 42C, 42D, 43, 44, 45, 46, 47, 4A1, 4A2, 4B1A1, 4B1B, 4B2, 4B3, 4C1, 4C2, 5, 5A, 5B, 5C, 6, 7, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1890,6 +2030,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A, 15B, 15C, 16, 17, 18, 19, 1A1A, 1A1B1A1, 1A1B1A1A, 1A1B1B2A, 1A1B1C, 1A1B1C2A, 1A1B1C2B, 1A1B1C3, 1A1B2A, 1A2, 1B, 1C, 1D, 20, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 2A1A1, 2A1A2A, 2A1B, 2A1C, 2A2, 2A3, 2B1, 2B2, 2C, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 445, 45, 46, 47, 48, 49, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1897,6 +2042,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1A, 1A1A1B, 1A1A2, 1A1B1, 1A1B2, 1A2A, 1A2A2, 1A2B, 1B, 1C1, 1C2, 1C3, 20, 2A1A, 2A1B, 2A2, 2B1, 2B2, 2C1, 2C2, 2D1, 2D2, 3A1, 3A2, 3B, 3C1A1A, 3C1A2, 3C1A3, 3C1B, 3C2, 4A, 4B1A1A, 4B1B, 4B1C, 4B1D, 4B2A1, 4B2A2, 4B2B1A1A1, 4B2B2A, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1904,6 +2054,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B1C, 1B3, 1C1, 1C2A1, 1C2B, 2, 3A1A, 3A1B, 3A1C, 3A1D, 3A1E, 3A1F, 3A1G, 3A2A, 3A2B1A, 3A2B2, 3A2C, 3A2D, 3A2E, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1911,6 +2066,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1918,6 +2078,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B1, 1B2, 1C1, 1C2, 1C3, 2, 3A, 3B, 3C, 4A, 4B, 4C, 4D, 4E</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1925,6 +2090,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A, 1B1A1A1, 1B1A1B, 1B2, 1B3, 1B4, 1B5, 2A1, 2A2, 2B1, 2B2, 2C1A, 2C1B, 2C2A, 2C2B, 2C2C, 3A, 3B, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1932,6 +2102,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1939,6 +2114,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1A, 2B1B, 2B2A, 2B2B, 2C, 2D, 2E1A1A1, 2E1B, 2E2, 2F1, 2F2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1946,6 +2126,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A1A1, 1A2A1, 1A2B1, 1B, 2A1, 2A2A1, 2A2B, 2A2C, 2A2D, 2A2E, 2A2F, 2A2G, 2A2H, 2A2J, 2A2K, 2A2L1, 2A2L2, 2A2M, 2A2N, 2B, 2C1, 2C2, 2C3, 2C4, 2C5, 2C6, 2C7, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1953,6 +2138,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1960,6 +2150,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1967,6 +2162,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A1, 1A2, 1A3, 1B1A, 1B1B, 1B2, 2A1A, 2A1B, 2A2, 2A3, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1974,6 +2174,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>10, 100, 101, 102, 103, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A1B, 1A1C, 1A1D, 1A1E, 1A1F, 1A1G, 1A1H, 1A1I, 1A1J, 1A1K, 1A1L, 1A1M, 1A1N, 1A1P, 1A2, 1B, 20, 21A, 21B, 21C, 21D, 22A, 22B, 22C, 22D, 22E, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 7A1, 7A2, 7B, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1981,6 +2186,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A10, 1A1B, 1A1C, 1A2, 1A3, 1A4, 1A5, 1A6A, 1A7A1, 1A8, 1A9A, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1988,6 +2198,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1995,6 +2210,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2B, 2C, 3A, 3B, 3C, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 5K, 5L, 5M</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2002,6 +2222,11 @@
           <t>60A</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1B2, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2009,6 +2234,11 @@
           <t>60B</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 2, 2A, 2B1, 2B2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2016,6 +2246,11 @@
           <t>61A</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2023,6 +2258,11 @@
           <t>61B</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2030,6 +2270,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2037,6 +2282,11 @@
           <t>63A</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2044,6 +2294,11 @@
           <t>63B</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2051,6 +2306,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2058,6 +2318,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2065,6 +2330,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2072,6 +2342,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2079,6 +2354,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2086,6 +2366,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2093,6 +2378,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2100,6 +2390,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2107,6 +2402,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2114,6 +2414,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2121,6 +2426,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2128,6 +2438,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2135,6 +2450,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2142,6 +2462,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2149,6 +2474,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2156,6 +2486,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2163,6 +2498,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2170,6 +2510,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A1, 1A1A2, 1A1B, 1A2, 1B1, 1B2, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2177,6 +2522,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2184,6 +2534,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2191,6 +2546,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2198,6 +2558,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2205,6 +2570,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2212,6 +2582,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2219,6 +2594,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2226,6 +2606,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5A1, 5A2, 5B, 5C, 6A, 6B, 6C</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2233,6 +2618,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2240,6 +2630,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2247,6 +2642,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C1, 1C2, 2, 3A1, 3A2, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2254,6 +2654,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2261,6 +2666,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2B1, 2B2, 2D, 3A1, 3A2, 3B, 3C1, 3C2, 3C3, 4A, 4B1, 4B2, 4B3</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2268,6 +2678,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C1, 10C2, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 5C1, 5C2, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2275,6 +2690,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2282,6 +2702,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2289,6 +2714,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2296,6 +2726,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2303,6 +2738,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2310,11 +2750,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 9A, 9B</t>
         </is>
       </c>
     </row>
